--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132650643</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57101</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Löfdalsäng, Tullgarn, Vagnhärad , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>643299</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6539637</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Njunjes</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>132650643</v>
       </c>
       <c r="B4" t="n">
-        <v>57101</v>
+        <v>57105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1325079</v>
       </c>
       <c r="B2" t="n">
-        <v>90318</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642569.8790157672</v>
+        <v>642570</v>
       </c>
       <c r="R2" t="n">
-        <v>6540249.863915851</v>
+        <v>6540250</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2004-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81201762</v>
+        <v>133428799</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,27 +810,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dånsjömossen, Srm</t>
+          <t>Löfdalsäng, Tullgarn, Vagnhärad , Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642942.229584921</v>
+        <v>643299</v>
       </c>
       <c r="R3" t="n">
-        <v>6539967.511544192</v>
+        <v>6539637</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,19 +880,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Johan Njunjes</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Johan Njunjes</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -920,11 +901,11 @@
         <v>132650643</v>
       </c>
       <c r="B4" t="n">
-        <v>57108</v>
+        <v>57125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1038,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133428799</v>
+        <v>134469119</v>
       </c>
       <c r="B5" t="n">
-        <v>57921</v>
+        <v>61527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,16 +1030,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>106670</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,34 +1047,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Löfdalsäng, Tullgarn, Vagnhärad , Srm</t>
+          <t>Fädrevsberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>643299</v>
+        <v>643121</v>
       </c>
       <c r="R5" t="n">
-        <v>6539637</v>
+        <v>6539912</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1114,232 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Njunjes</t>
+          <t>Hanna Mellgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Njunjes</t>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>81201762</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dånsjömossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>642942</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539968</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134469722</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fädrevsberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>643121</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539912</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81201762</v>
+        <v>134470270</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,49 +1137,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dånsjömossen, Srm</t>
+          <t>Fädrevsberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>642942</v>
+        <v>643121</v>
       </c>
       <c r="R6" t="n">
-        <v>6539968</v>
+        <v>6539912</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,12 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,29 +1215,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Hanna Mellgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134469722</v>
+        <v>81201762</v>
       </c>
       <c r="B7" t="n">
-        <v>98063</v>
+        <v>99022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,37 +1244,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fädrevsberget, Srm</t>
+          <t>Dånsjömossen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>643121</v>
+        <v>642942</v>
       </c>
       <c r="R7" t="n">
-        <v>6539912</v>
+        <v>6539968</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,22 +1310,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,21 +1324,129 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134469722</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fädrevsberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>643121</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6539912</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Hanna Mellgren</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134469119</v>
+        <v>134622674</v>
       </c>
       <c r="B5" t="n">
-        <v>61527</v>
+        <v>57125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,37 +1030,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106670</v>
+        <v>102932</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fädrevsberget, Srm</t>
+          <t>Löfdalsäng, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>643121</v>
+        <v>643264</v>
       </c>
       <c r="R5" t="n">
-        <v>6539912</v>
+        <v>6539611</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1096,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1094,12 +1106,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,44 +1126,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hanna Mellgren</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hanna Mellgren, Alexandra Holmgren</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134470270</v>
+        <v>134469119</v>
       </c>
       <c r="B6" t="n">
-        <v>99112</v>
+        <v>61527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>106670</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81201762</v>
+        <v>134470270</v>
       </c>
       <c r="B7" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,49 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dånsjömossen, Srm</t>
+          <t>Fädrevsberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>642942</v>
+        <v>643121</v>
       </c>
       <c r="R7" t="n">
-        <v>6539968</v>
+        <v>6539912</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,12 +1310,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,29 +1334,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Hanna Mellgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134469722</v>
+        <v>81201762</v>
       </c>
       <c r="B8" t="n">
-        <v>98063</v>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,37 +1363,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fädrevsberget, Srm</t>
+          <t>Dånsjömossen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>643121</v>
+        <v>642942</v>
       </c>
       <c r="R8" t="n">
-        <v>6539912</v>
+        <v>6539968</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,22 +1429,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,21 +1443,129 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134469722</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fädrevsberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>643121</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6539912</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Hanna Mellgren</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hanna Mellgren, Alexandra Holmgren</t>
+          <t>Alexandra Holmgren, Hanna Mellgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren, Hanna Mellgren</t>
+          <t>Hanna Mellgren, Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 48791-2024 artfynd.xlsx
+++ b/artfynd/A 48791-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1325079</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133428799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132650643</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134622674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134469119</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134470270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81201762</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,8 +1606,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134469722</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>